--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_17-08-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_17-08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9EBCF6-89F8-4303-A30D-7CF84605ADBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9050F59B-E2F2-4170-B520-D21CF751BA04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33735" yWindow="1365" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33735" yWindow="2685" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -691,48 +691,6 @@
     <t>£795.39</t>
   </si>
   <si>
-    <t>£17.75</t>
-  </si>
-  <si>
-    <t>£21.50</t>
-  </si>
-  <si>
-    <t>£23.25</t>
-  </si>
-  <si>
-    <t>£27.75</t>
-  </si>
-  <si>
-    <t>£31.50</t>
-  </si>
-  <si>
-    <t>£31.75</t>
-  </si>
-  <si>
-    <t>£35.25</t>
-  </si>
-  <si>
-    <t>£38.25</t>
-  </si>
-  <si>
-    <t>£39.75</t>
-  </si>
-  <si>
-    <t>£47.00</t>
-  </si>
-  <si>
-    <t>£48.75</t>
-  </si>
-  <si>
-    <t>£56.50</t>
-  </si>
-  <si>
-    <t>£59.75</t>
-  </si>
-  <si>
-    <t>£58.25</t>
-  </si>
-  <si>
     <t>£43.70</t>
   </si>
   <si>
@@ -803,6 +761,48 @@
   </si>
   <si>
     <t>£716.05</t>
+  </si>
+  <si>
+    <t>£14.50</t>
+  </si>
+  <si>
+    <t>£17.00</t>
+  </si>
+  <si>
+    <t>£20.50</t>
+  </si>
+  <si>
+    <t>£22.00</t>
+  </si>
+  <si>
+    <t>£26.50</t>
+  </si>
+  <si>
+    <t>£30.00</t>
+  </si>
+  <si>
+    <t>£34.00</t>
+  </si>
+  <si>
+    <t>£36.50</t>
+  </si>
+  <si>
+    <t>£37.50</t>
+  </si>
+  <si>
+    <t>£45.00</t>
+  </si>
+  <si>
+    <t>£46.50</t>
+  </si>
+  <si>
+    <t>£52.50</t>
+  </si>
+  <si>
+    <t>£57.50</t>
+  </si>
+  <si>
+    <t>£55.00</t>
   </si>
 </sst>
 </file>
@@ -1241,7 +1241,7 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>247</v>
       </c>
       <c r="G2" t="s">
         <v>21</v>
@@ -1297,7 +1297,7 @@
         <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="G3" t="s">
         <v>36</v>
@@ -1321,7 +1321,7 @@
         <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="O3" t="s">
         <v>42</v>
@@ -1353,7 +1353,7 @@
         <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="G4" t="s">
         <v>48</v>
@@ -1377,7 +1377,7 @@
         <v>53</v>
       </c>
       <c r="N4" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="O4" t="s">
         <v>54</v>
@@ -1409,7 +1409,7 @@
         <v>58</v>
       </c>
       <c r="F5" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="G5" t="s">
         <v>59</v>
@@ -1433,7 +1433,7 @@
         <v>63</v>
       </c>
       <c r="N5" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="O5" t="s">
         <v>64</v>
@@ -1465,7 +1465,7 @@
         <v>69</v>
       </c>
       <c r="F6" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="G6" t="s">
         <v>70</v>
@@ -1477,7 +1477,7 @@
         <v>72</v>
       </c>
       <c r="J6" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="K6" t="s">
         <v>73</v>
@@ -1489,7 +1489,7 @@
         <v>74</v>
       </c>
       <c r="N6" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="O6" t="s">
         <v>75</v>
@@ -1521,7 +1521,7 @@
         <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="G7" t="s">
         <v>80</v>
@@ -1533,7 +1533,7 @@
         <v>82</v>
       </c>
       <c r="J7" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="K7" t="s">
         <v>83</v>
@@ -1577,7 +1577,7 @@
         <v>89</v>
       </c>
       <c r="F8" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="G8" t="s">
         <v>89</v>
@@ -1601,7 +1601,7 @@
         <v>93</v>
       </c>
       <c r="N8" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="O8" t="s">
         <v>94</v>
@@ -1633,7 +1633,7 @@
         <v>98</v>
       </c>
       <c r="F9" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="G9" t="s">
         <v>99</v>
@@ -1657,7 +1657,7 @@
         <v>104</v>
       </c>
       <c r="N9" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="O9" t="s">
         <v>105</v>
@@ -1689,7 +1689,7 @@
         <v>110</v>
       </c>
       <c r="F10" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="G10" t="s">
         <v>111</v>
@@ -1701,7 +1701,7 @@
         <v>30</v>
       </c>
       <c r="J10" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="K10" t="s">
         <v>103</v>
@@ -1745,7 +1745,7 @@
         <v>110</v>
       </c>
       <c r="F11" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="G11" t="s">
         <v>117</v>
@@ -1769,7 +1769,7 @@
         <v>121</v>
       </c>
       <c r="N11" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="O11" t="s">
         <v>122</v>
@@ -1801,7 +1801,7 @@
         <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="G12" t="s">
         <v>128</v>
@@ -1857,7 +1857,7 @@
         <v>135</v>
       </c>
       <c r="F13" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="G13" t="s">
         <v>136</v>
@@ -1869,7 +1869,7 @@
         <v>138</v>
       </c>
       <c r="J13" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="K13" t="s">
         <v>139</v>
@@ -1881,7 +1881,7 @@
         <v>140</v>
       </c>
       <c r="N13" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="O13" t="s">
         <v>141</v>
@@ -1913,7 +1913,7 @@
         <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="G14" t="s">
         <v>146</v>
@@ -1925,7 +1925,7 @@
         <v>148</v>
       </c>
       <c r="J14" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="K14" t="s">
         <v>149</v>
@@ -1937,7 +1937,7 @@
         <v>150</v>
       </c>
       <c r="N14" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="O14" t="s">
         <v>151</v>
@@ -1969,7 +1969,7 @@
         <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="G15" t="s">
         <v>155</v>
@@ -1981,7 +1981,7 @@
         <v>157</v>
       </c>
       <c r="J15" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="K15" t="s">
         <v>158</v>
@@ -1993,7 +1993,7 @@
         <v>159</v>
       </c>
       <c r="N15" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="O15" t="s">
         <v>160</v>
@@ -2025,7 +2025,7 @@
         <v>164</v>
       </c>
       <c r="F16" t="s">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="G16" t="s">
         <v>165</v>
@@ -2037,7 +2037,7 @@
         <v>167</v>
       </c>
       <c r="J16" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="K16" t="s">
         <v>168</v>
@@ -2049,7 +2049,7 @@
         <v>169</v>
       </c>
       <c r="N16" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="O16" t="s">
         <v>170</v>
@@ -2205,7 +2205,7 @@
         <v>26</v>
       </c>
       <c r="J19" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="K19" t="s">
         <v>26</v>
@@ -2373,7 +2373,7 @@
         <v>26</v>
       </c>
       <c r="J22" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="K22" t="s">
         <v>26</v>
@@ -2432,7 +2432,7 @@
         <v>26</v>
       </c>
       <c r="K23" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="L23" t="s">
         <v>26</v>
@@ -2441,7 +2441,7 @@
         <v>206</v>
       </c>
       <c r="N23" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="O23" t="s">
         <v>207</v>
@@ -2488,7 +2488,7 @@
         <v>26</v>
       </c>
       <c r="K24" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="L24" t="s">
         <v>26</v>
@@ -2497,7 +2497,7 @@
         <v>30</v>
       </c>
       <c r="N24" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="O24" t="s">
         <v>213</v>
@@ -2553,7 +2553,7 @@
         <v>30</v>
       </c>
       <c r="N25" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="O25" t="s">
         <v>221</v>
